--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5316</v>
+        <v>5448</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>50.8</v>
+        <v>46.9</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>12.9</v>
+        <v>14.8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>23.2</v>
+        <v>29.6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>86.90000000000001</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1342</v>
+        <v>1306</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="5">
@@ -567,16 +567,16 @@
         <v>930</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1616</v>
+        <v>1406</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>2.8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>845</v>
+        <v>805</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>3.2</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6323</v>
+        <v>6423</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>83</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.9</v>
+        <v>21.6</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0.9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>104.8</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2350</v>
+        <v>2320</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>16.6</v>
+        <v>15.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>28.6</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5900</v>
+        <v>5500</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>38.4</v>
+        <v>34.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>22.7</v>
+        <v>21.9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>61.1</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4247</v>
+        <v>4731</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17.6</v>
+        <v>22.5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>75.7</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3572</v>
+        <v>3752</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>39.4</v>
+        <v>41</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>44.9</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1684</v>
+        <v>1739</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2775</v>
+        <v>2600</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>76.8</v>
+        <v>70.2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>100.7</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="16">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2296</v>
+        <v>2196</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>62.6</v>
+        <v>57.6</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>17.2</v>
@@ -818,7 +818,7 @@
         <v>23</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>102.9</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1279</v>
+        <v>1247</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>24.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>30.4</v>
+        <v>29.7</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>54.8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
@@ -853,16 +853,16 @@
         <v>2560</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>51.8</v>
+        <v>53.9</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>43.1</v>
+        <v>41.5</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3430</v>
+        <v>3530</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>27.2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2554</v>
+        <v>2454</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>5</v>
@@ -906,7 +906,7 @@
         <v>1.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1257</v>
+        <v>1147</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>22.7</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17.3</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>91.7</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>115.5</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3029</v>
+        <v>3145</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>26.5</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1200</v>
+        <v>1305</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>64615</v>
+        <v>64604</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>610.7</v>
+        <v>589.1</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>290.8</v>
+        <v>297</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>157.1</v>
+        <v>163.9</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1058.6</v>
+        <v>1049.9</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3250</v>
+        <v>3000</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>50.8</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>12.9</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>666</v>
+        <v>848</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>23.2</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>880</v>
+        <v>750</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>730</v>
+        <v>650</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="16">
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2.1</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0.1</v>
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>20.9</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="23">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>16.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1100</v>
+        <v>1120</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>38.4</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>22.7</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2300</v>
+        <v>2280</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>17.6</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2050</v>
+        <v>2130</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>39.4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1520</v>
+        <v>1620</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="38">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1750</v>
+        <v>1600</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>76.8</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1250</v>
+        <v>1150</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>50.1</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>62.6</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="43">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>38</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>30.4</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="47">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>2.6</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>51.8</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>43.1</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1630</v>
+        <v>1670</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1800</v>
+        <v>1860</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>710</v>
+        <v>680</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="59">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="62">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1550</v>
+        <v>1615</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>4.7</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>949</v>
+        <v>990</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>650</v>
+        <v>610</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>550</v>
+        <v>695</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="71">
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>610.7</v>
+        <v>589.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>290.8</v>
+        <v>297</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>157.1</v>
+        <v>163.9</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1058.6</v>
+        <v>1049.9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11771.4</v>
+        <v>11762.8</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7525.7</v>
+        <v>7504</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2695.9</v>
+        <v>2702.1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1549.9</v>
+        <v>1556.6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11771.4</v>
+        <v>11762.8</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11771.4</v>
+        <v>11762.8</v>
       </c>
     </row>
   </sheetData>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.08.pdf</t>
+          <t>Revenue Meeting_2026.09.15.pdf</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.09.08</t>
+          <t>2026.09.15</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>589.1</v>
+        <v>610.7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>297</v>
+        <v>290.8</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>163.9</v>
+        <v>157.1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1049.9</v>
+        <v>1058.6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11762.8</v>
+        <v>11771.4</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7504</v>
+        <v>7525.7</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2702.1</v>
+        <v>2695.9</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1556.6</v>
+        <v>1549.9</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11762.8</v>
+        <v>11771.4</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11762.8</v>
+        <v>11771.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>610.7</v>
+        <v>589.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>290.8</v>
+        <v>297</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>157.1</v>
+        <v>163.9</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1058.6</v>
+        <v>1049.9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11771.4</v>
+        <v>11762.8</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7525.7</v>
+        <v>7504</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2695.9</v>
+        <v>2702.1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1549.9</v>
+        <v>1556.6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11771.4</v>
+        <v>11762.8</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11771.4</v>
+        <v>11762.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5448</v>
+        <v>4555</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>46.9</v>
+        <v>37.5</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>14.8</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>91.2</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1306</v>
+        <v>1196</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>20.1</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>930</v>
+        <v>840</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1406</v>
+        <v>1246</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>2.8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>805</v>
+        <v>770</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8">
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2320</v>
+        <v>2100</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>15.9</v>
+        <v>14.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>28.2</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5500</v>
+        <v>5050</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>34.5</v>
+        <v>32</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>21.9</v>
+        <v>20</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>56.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4731</v>
+        <v>4703</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3752</v>
+        <v>3812</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="14">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1739</v>
+        <v>1709</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>9.1</v>
@@ -774,7 +774,7 @@
         <v>0.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="15">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2600</v>
+        <v>2650</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>70.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>23.4</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>93.5</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2196</v>
+        <v>2166</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>57.6</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1247</v>
+        <v>1166</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>24.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>29.7</v>
+        <v>26.6</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>54</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2560</v>
+        <v>2460</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>53.9</v>
+        <v>52.6</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>41.5</v>
+        <v>39.2</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>95.7</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3530</v>
+        <v>3500</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2454</v>
+        <v>2404</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1147</v>
+        <v>1067</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>12.9</v>
+        <v>11.4</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>20.6</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6400</v>
+        <v>5650</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>17.3</v>
+        <v>13.9</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>91.7</v>
+        <v>86.2</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>115.2</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3145</v>
+        <v>3176</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>16.6</v>
+        <v>18.5</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>7.6</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3000</v>
+        <v>2960</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1305</v>
+        <v>1320</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>64604</v>
+        <v>61631</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>589.1</v>
+        <v>574.3</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>297</v>
+        <v>279.4</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>163.9</v>
+        <v>159.3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1049.9</v>
+        <v>1013</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>46.9</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>14.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>880</v>
+        <v>810</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>750</v>
+        <v>680</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>650</v>
+        <v>560</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>15.9</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1120</v>
+        <v>1000</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>34.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2800</v>
+        <v>2550</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>21.9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2280</v>
+        <v>2300</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2130</v>
+        <v>2160</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>41</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1620</v>
+        <v>1650</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>930</v>
+        <v>900</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="37">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>70.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>16.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="44">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>780</v>
+        <v>700</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>38</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>29.7</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="47">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>2.6</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1250</v>
+        <v>1220</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>53.9</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>41.5</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1670</v>
+        <v>1700</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1860</v>
+        <v>1800</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="53">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.9</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="56">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>12.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>17.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>17.3</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2500</v>
+        <v>2350</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>36.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>91.7</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>16.6</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="64">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>4.7</v>
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>990</v>
+        <v>956</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="66">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1600</v>
+        <v>1560</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="71">
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>589.1</v>
+        <v>574.3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>297</v>
+        <v>279.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>163.9</v>
+        <v>159.3</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1049.9</v>
+        <v>1013</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11762.8</v>
+        <v>11725.9</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7504</v>
+        <v>7489.2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2702.1</v>
+        <v>2684.6</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1556.6</v>
+        <v>1552.1</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11762.8</v>
+        <v>11725.9</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11762.8</v>
+        <v>11725.9</v>
       </c>
     </row>
   </sheetData>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.15.pdf</t>
+          <t>Revenue Meeting_2026.09.22.pdf</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.09.15</t>
+          <t>2026.09.22</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4555</v>
+        <v>5448</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>37.5</v>
+        <v>46.9</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>12</v>
+        <v>14.8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>79.3</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1196</v>
+        <v>1306</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>18.7</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>840</v>
+        <v>930</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1246</v>
+        <v>1406</v>
       </c>
       <c r="C6" s="4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>6.3</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>5.4</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>2.8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>770</v>
+        <v>805</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="8">
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>708</v>
+        <v>660</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2100</v>
+        <v>2320</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>14.6</v>
+        <v>15.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>25.5</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5050</v>
+        <v>5500</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>32</v>
+        <v>34.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>20</v>
+        <v>21.9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>51.9</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4703</v>
+        <v>4731</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3812</v>
+        <v>3752</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>41.6</v>
+        <v>41</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>47.5</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="14">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1709</v>
+        <v>1739</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>9.1</v>
@@ -774,7 +774,7 @@
         <v>0.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="15">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2650</v>
+        <v>2600</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>23.4</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>95.7</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2166</v>
+        <v>2196</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>57.6</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>97.3</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1166</v>
+        <v>1247</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>24.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>26.6</v>
+        <v>29.7</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>50.9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2460</v>
+        <v>2560</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>52.6</v>
+        <v>53.9</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>39.2</v>
+        <v>41.5</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>92.2</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3500</v>
+        <v>3530</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2404</v>
+        <v>2454</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1067</v>
+        <v>1147</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>19.1</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5650</v>
+        <v>6400</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>13.9</v>
+        <v>17.3</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>86.2</v>
+        <v>91.7</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>105.4</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3176</v>
+        <v>3145</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>7.6</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>29</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2960</v>
+        <v>3000</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1320</v>
+        <v>1305</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>61631</v>
+        <v>64604</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>574.3</v>
+        <v>589.1</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>279.4</v>
+        <v>297</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>159.3</v>
+        <v>163.9</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1013</v>
+        <v>1049.9</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>37.5</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>12</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>810</v>
+        <v>880</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>560</v>
+        <v>650</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>14.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1000</v>
+        <v>1120</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>32</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2550</v>
+        <v>2800</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>20</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2300</v>
+        <v>2280</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2160</v>
+        <v>2130</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>41.6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1650</v>
+        <v>1620</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="40">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>16.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="44">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>700</v>
+        <v>780</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>38</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>26.6</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="47">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>2.6</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1220</v>
+        <v>1250</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>52.6</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1230</v>
+        <v>1300</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>39.2</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1700</v>
+        <v>1670</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1800</v>
+        <v>1860</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="53">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.9</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>17.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>13.9</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2350</v>
+        <v>2500</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>36.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>86.2</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="64">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>4.7</v>
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>956</v>
+        <v>990</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1560</v>
+        <v>1600</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>650</v>
+        <v>610</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="71">
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>574.3</v>
+        <v>589.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>279.4</v>
+        <v>297</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>159.3</v>
+        <v>163.9</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1013</v>
+        <v>1049.9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11725.9</v>
+        <v>11762.8</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7489.2</v>
+        <v>7504</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2684.6</v>
+        <v>2702.1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1552.1</v>
+        <v>1556.6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11725.9</v>
+        <v>11762.8</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11725.9</v>
+        <v>11762.8</v>
       </c>
     </row>
   </sheetData>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.22.pdf</t>
+          <t>Revenue Meeting_2026.09.15.pdf</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.09.22</t>
+          <t>2026.09.15</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5448</v>
+        <v>4555</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>46.9</v>
+        <v>37.5</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>14.8</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>91.2</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1306</v>
+        <v>1196</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>20.1</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>930</v>
+        <v>840</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1406</v>
+        <v>1246</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>2.8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>805</v>
+        <v>770</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8">
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2320</v>
+        <v>2100</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>15.9</v>
+        <v>14.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>28.2</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5500</v>
+        <v>5050</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>34.5</v>
+        <v>32</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>21.9</v>
+        <v>20</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>56.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4731</v>
+        <v>4703</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3752</v>
+        <v>3812</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="14">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1739</v>
+        <v>1709</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>9.1</v>
@@ -774,7 +774,7 @@
         <v>0.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="15">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2600</v>
+        <v>2650</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>70.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>23.4</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>93.5</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2196</v>
+        <v>2166</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>57.6</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1247</v>
+        <v>1166</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>24.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>29.7</v>
+        <v>26.6</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>54</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2560</v>
+        <v>2460</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>53.9</v>
+        <v>52.6</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>41.5</v>
+        <v>39.2</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>95.7</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3530</v>
+        <v>3500</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2454</v>
+        <v>2404</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1147</v>
+        <v>1067</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>12.9</v>
+        <v>11.4</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>20.6</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6400</v>
+        <v>5650</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>17.3</v>
+        <v>13.9</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>91.7</v>
+        <v>86.2</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>115.2</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3145</v>
+        <v>3176</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>16.6</v>
+        <v>18.5</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>7.6</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3000</v>
+        <v>2960</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1305</v>
+        <v>1320</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>64604</v>
+        <v>61631</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>589.1</v>
+        <v>574.3</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>297</v>
+        <v>279.4</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>163.9</v>
+        <v>159.3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1049.9</v>
+        <v>1013</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>46.9</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>14.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>880</v>
+        <v>810</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>750</v>
+        <v>680</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>650</v>
+        <v>560</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>15.9</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1120</v>
+        <v>1000</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>34.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2800</v>
+        <v>2550</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>21.9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2280</v>
+        <v>2300</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2130</v>
+        <v>2160</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>41</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1620</v>
+        <v>1650</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>930</v>
+        <v>900</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="37">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>70.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>16.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="44">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>780</v>
+        <v>700</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>38</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>29.7</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="47">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>2.6</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1250</v>
+        <v>1220</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>53.9</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>41.5</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1670</v>
+        <v>1700</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1860</v>
+        <v>1800</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="53">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.9</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="56">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>12.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>17.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>17.3</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2500</v>
+        <v>2350</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>36.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>91.7</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>16.6</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="64">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>4.7</v>
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>990</v>
+        <v>956</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="66">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1600</v>
+        <v>1560</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="71">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.15.pdf</t>
+          <t>Revenue Meeting_2026.09.22.pdf</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.09.15</t>
+          <t>2026.09.22</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>589.1</v>
+        <v>574.3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>297</v>
+        <v>279.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>163.9</v>
+        <v>159.3</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1049.9</v>
+        <v>1013</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11762.8</v>
+        <v>11725.9</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7504</v>
+        <v>7489.2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2702.1</v>
+        <v>2684.6</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1556.6</v>
+        <v>1552.1</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11762.8</v>
+        <v>11725.9</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11762.8</v>
+        <v>11725.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.22.pdf</t>
+          <t>Revenue Meeting_2026.09.29.pdf</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.09.22</t>
+          <t>2026.09.29</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.29.pdf</t>
+          <t>Revenue Meeting_2026.09.22.pdf</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.09.29</t>
+          <t>2026.09.22</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.22.pdf</t>
+          <t>Revenue Meeting_2026.09.29.pdf</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.09.22</t>
+          <t>2026.09.29</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 예상매출 - 2026-09  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
+          <t>소사업 예상매출 - 2026-10  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4555</v>
+        <v>4382</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>37.5</v>
+        <v>30.3</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>29.8</v>
+        <v>8.1</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>79.3</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1196</v>
+        <v>900</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1246</v>
+        <v>1750</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.5</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>770</v>
+        <v>950</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>708</v>
+        <v>777</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6423</v>
+        <v>6854</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>83</v>
+        <v>75.7</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>21.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>105.5</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>14.6</v>
+        <v>16.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>25.5</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5050</v>
+        <v>4262</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>20</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>51.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4703</v>
+        <v>5384</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>51.9</v>
+        <v>30.3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>22</v>
+        <v>7.1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3812</v>
+        <v>3062</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>41.6</v>
+        <v>29.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>47.5</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1709</v>
+        <v>2590</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9.1</v>
+        <v>21.2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18.2</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2650</v>
+        <v>2100</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>59.2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>23.4</v>
+        <v>17.5</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>95.7</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2166</v>
+        <v>2330</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>57.6</v>
+        <v>60.3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>23</v>
+        <v>11.2</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>97.3</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1166</v>
+        <v>1543</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>24.1</v>
+        <v>15.3</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>26.6</v>
+        <v>14.1</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>50.9</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2460</v>
+        <v>2428</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>52.6</v>
+        <v>34.5</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>39.2</v>
+        <v>12.6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>92.2</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3500</v>
+        <v>3362</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>13.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>27.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2404</v>
+        <v>2226</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1067</v>
+        <v>1310</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>7.7</v>
+        <v>14.2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>19.1</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5650</v>
+        <v>7150</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>13.9</v>
+        <v>10.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>86.2</v>
+        <v>132.1</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>105.4</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3176</v>
+        <v>3773</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>18.5</v>
+        <v>3.7</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>29</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2960</v>
+        <v>2753</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1320</v>
+        <v>1205</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>61631</v>
+        <v>63941</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>574.3</v>
+        <v>467.9</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>279.4</v>
+        <v>201.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>159.3</v>
+        <v>170.5</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1013</v>
+        <v>840.1</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 세그먼트별 - 2026-09</t>
+          <t>소사업 세그먼트별 - 2026-10</t>
         </is>
       </c>
     </row>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>15.6</v>
+        <v>11.2</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>37.5</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1300</v>
+        <v>1450</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>855</v>
+        <v>232</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>29.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>810</v>
+        <v>550</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>15.6</v>
+        <v>11.2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>15.6</v>
+        <v>11.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>680</v>
+        <v>900</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.3</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>560</v>
+        <v>850</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>310</v>
+        <v>450</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19">
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>330</v>
+        <v>400</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>25.2</v>
+        <v>21</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>83</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>21.6</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>39</v>
+        <v>43.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -1550,10 +1550,10 @@
         <v>1100</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>13.3</v>
+        <v>15.1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>14.6</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="26">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0</v>
+        <v>20.6</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>0</v>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2500</v>
+        <v>2350</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2550</v>
+        <v>1900</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>20</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>55.9</v>
+        <v>27.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2300</v>
+        <v>2830</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>22.6</v>
+        <v>10.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>51.9</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2250</v>
+        <v>2280</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>22</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>153</v>
+        <v>274</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>42.5</v>
+        <v>3.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2160</v>
+        <v>1550</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>41.6</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="35">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="36">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>900</v>
+        <v>1310</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>800</v>
+        <v>1250</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>11.4</v>
+        <v>17</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>9.1</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>45.4</v>
+        <v>45</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1650</v>
+        <v>1350</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>23.4</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1150</v>
+        <v>1270</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>50.1</v>
+        <v>47.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>57.6</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="43">
@@ -1949,10 +1949,10 @@
         <v>1000</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="44">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1440</v>
+        <v>186.1</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>23</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="45">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>60.3</v>
+        <v>35.5</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>24.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>38</v>
+        <v>15.6</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>26.6</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>2.6</v>
+        <v>28.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>43.2</v>
+        <v>26.5</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>52.6</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1230</v>
+        <v>1100</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>31.9</v>
+        <v>11.5</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>39.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="50">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>27.3</v>
+        <v>14.1</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="51">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>13.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1800</v>
+        <v>1760</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="53">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>37.8</v>
+        <v>124.1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="54">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1650</v>
+        <v>1400</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>19.2</v>
+        <v>25.8</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>7.7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>600</v>
+        <v>760</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="59">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>0</v>
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>800</v>
+        <v>950</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>17.3</v>
+        <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>13.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2350</v>
+        <v>3500</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>36.7</v>
+        <v>37.8</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>86.2</v>
+        <v>132.1</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>30.8</v>
+        <v>5.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>18.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1620</v>
+        <v>1700</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>956</v>
+        <v>1423</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="66">
@@ -2432,10 +2432,10 @@
         <v>1400</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1560</v>
+        <v>1350</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="68">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>58.6</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="69">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>670</v>
+        <v>550</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="71">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2566,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 월별 누적 - 2026-09 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+          <t>소사업 월별 누적 - 2026-10 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
         </is>
       </c>
     </row>
@@ -2831,46 +2831,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>온북</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>542.6</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>271.9</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>11684.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10월</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>RM FCST</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>574.3</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>279.4</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>159.3</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1013</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>11725.9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="n">
+        <v>467.9</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>201.7</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>840.1</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>12524.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="7" t="n">
-        <v>7489.2</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>2684.6</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>1552.1</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>11725.9</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>11725.9</v>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="7" t="n">
+        <v>7925.5</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2878.7</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>1720.5</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>12524.7</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>12524.7</v>
       </c>
     </row>
   </sheetData>
@@ -2899,7 +2926,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2938,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전년 2025-09 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-10 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 예상매출 - 2026-10  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
+          <t>소사업 예상매출 - 2026-09  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4382</v>
+        <v>4555</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>30.3</v>
+        <v>37.5</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>8.1</v>
+        <v>29.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>48.8</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>900</v>
+        <v>1196</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6.2</v>
+        <v>12.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1750</v>
+        <v>1246</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>16.1</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>950</v>
+        <v>770</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8">
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>777</v>
+        <v>708</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6854</v>
+        <v>6423</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>75.7</v>
+        <v>83</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>15.3</v>
+        <v>21.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>21.7</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4262</v>
+        <v>5050</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>20</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>36.5</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5384</v>
+        <v>4703</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>30.3</v>
+        <v>51.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.1</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>38.3</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3062</v>
+        <v>3812</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>29.8</v>
+        <v>41.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>35.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2590</v>
+        <v>1709</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>21.2</v>
+        <v>9.1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>32.9</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2100</v>
+        <v>2650</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>59.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>17.5</v>
+        <v>23.4</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>76.7</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2330</v>
+        <v>2166</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>60.3</v>
+        <v>57.6</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>11.2</v>
+        <v>23</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>90.2</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1543</v>
+        <v>1166</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>15.3</v>
+        <v>24.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>14.1</v>
+        <v>26.6</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.1</v>
+        <v>0.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>35.4</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2428</v>
+        <v>2460</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>34.5</v>
+        <v>52.6</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>12.6</v>
+        <v>39.2</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>47.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3362</v>
+        <v>3500</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>13.9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>16.4</v>
+        <v>13.8</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>26</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2226</v>
+        <v>2404</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1310</v>
+        <v>1067</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>14.2</v>
+        <v>7.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>24.9</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7150</v>
+        <v>5650</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>10.1</v>
+        <v>13.9</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>132.1</v>
+        <v>86.2</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>147.8</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3773</v>
+        <v>3176</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.7</v>
+        <v>18.5</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>11.4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2753</v>
+        <v>2960</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.7</v>
+        <v>6.9</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1205</v>
+        <v>1320</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>63941</v>
+        <v>61631</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>467.9</v>
+        <v>574.3</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>201.7</v>
+        <v>279.4</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>170.5</v>
+        <v>159.3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>840.1</v>
+        <v>1013</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 세그먼트별 - 2026-10</t>
+          <t>소사업 세그먼트별 - 2026-09</t>
         </is>
       </c>
     </row>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>11.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>30.3</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1450</v>
+        <v>1300</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>232</v>
+        <v>855</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>8.1</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>550</v>
+        <v>810</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.2</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>900</v>
+        <v>680</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>850</v>
+        <v>560</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="14">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>10.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>450</v>
+        <v>310</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3600</v>
+        <v>3300</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>21</v>
+        <v>25.2</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>75.7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>15.3</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>43.3</v>
+        <v>39</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -1550,10 +1550,10 @@
         <v>1100</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>15.1</v>
+        <v>13.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>0</v>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2350</v>
+        <v>2500</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>11.8</v>
+        <v>12.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1900</v>
+        <v>2550</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>27.3</v>
+        <v>55.9</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2830</v>
+        <v>2300</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>10.7</v>
+        <v>22.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>30.3</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2280</v>
+        <v>2250</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>274</v>
+        <v>153</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.5</v>
+        <v>42.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1550</v>
+        <v>2160</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>29.8</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="35">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1310</v>
+        <v>900</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1250</v>
+        <v>800</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>17</v>
+        <v>11.4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>21.2</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>59.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>17.5</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1270</v>
+        <v>1150</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>47.5</v>
+        <v>50.1</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>60.3</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="43">
@@ -1949,10 +1949,10 @@
         <v>1000</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="44">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>186.1</v>
+        <v>1440</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>11.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>35.5</v>
+        <v>60.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>15.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>15.6</v>
+        <v>38</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>14.1</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>213</v>
+        <v>66</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>28.7</v>
+        <v>2.6</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>6.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>26.5</v>
+        <v>43.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>34.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1100</v>
+        <v>1230</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>11.5</v>
+        <v>31.9</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>12.6</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="50">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>14.1</v>
+        <v>27.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="51">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1760</v>
+        <v>1800</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>16.4</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="53">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>124.1</v>
+        <v>37.8</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="56">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>25.8</v>
+        <v>19.2</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>14.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>760</v>
+        <v>600</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="59">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>0</v>
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>10.7</v>
+        <v>17.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>10.1</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3500</v>
+        <v>2350</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>37.8</v>
+        <v>36.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>132.1</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>5.8</v>
+        <v>30.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>3.7</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1700</v>
+        <v>1620</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1423</v>
+        <v>956</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="66">
@@ -2432,10 +2432,10 @@
         <v>1400</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1350</v>
+        <v>1560</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>4.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="68">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>58.6</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>550</v>
+        <v>670</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="71">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2566,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 월별 누적 - 2026-10 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+          <t>소사업 월별 누적 - 2026-09 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
         </is>
       </c>
     </row>
@@ -2831,73 +2831,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>온북</t>
+          <t>RM FCST</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>542.6</v>
+        <v>574.3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>271.9</v>
+        <v>279.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>157.3</v>
+        <v>159.3</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>971.8</v>
+        <v>1013</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11684.6</v>
+        <v>11725.9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10월</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RM FCST</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>467.9</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>201.7</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>170.5</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>840.1</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>12524.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="7" t="n">
-        <v>7925.5</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>2878.7</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>1720.5</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>12524.7</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>12524.7</v>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="7" t="n">
+        <v>7489.2</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2684.6</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1552.1</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>11725.9</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>11725.9</v>
       </c>
     </row>
   </sheetData>
@@ -2926,7 +2899,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2911,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전년 2025-10 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-09 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2619,19 +2619,19 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>836.4</v>
+        <v>1671.2</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>287.3</v>
+        <v>573.5</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>139.3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1263</v>
+        <v>2384</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1263</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="4">
@@ -2646,19 +2646,19 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1102.3</v>
+        <v>2204.6</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>400.6</v>
+        <v>801.3</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>214.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1717.3</v>
+        <v>3220.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2980.3</v>
+        <v>5604.3</v>
       </c>
     </row>
     <row r="5">
@@ -2673,19 +2673,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>430.5</v>
+        <v>861</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>193.3</v>
+        <v>386.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>184.5</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>808.3</v>
+        <v>1432.1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>3788.5</v>
+        <v>7036.3</v>
       </c>
     </row>
     <row r="6">
@@ -2700,19 +2700,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>740.2</v>
+        <v>1480.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>224.1</v>
+        <v>448.3</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>261.9</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1226.2</v>
+        <v>2190.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5014.7</v>
+        <v>9226.799999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>814.9</v>
+        <v>1629.7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>183.1</v>
+        <v>366.1</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>163.7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1161.6</v>
+        <v>2159.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6176.3</v>
+        <v>11386.4</v>
       </c>
     </row>
     <row r="8">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>991.8</v>
+        <v>1983.5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>319.8</v>
+        <v>639.5</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>104.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1416.2</v>
+        <v>2727.7</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7592.5</v>
+        <v>14114.1</v>
       </c>
     </row>
     <row r="9">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>990</v>
+        <v>1980</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>369.6</v>
+        <v>739.2</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>182.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1541.8</v>
+        <v>2901.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9134.299999999999</v>
+        <v>17015.5</v>
       </c>
     </row>
     <row r="10">
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1009</v>
+        <v>1014.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>427.3</v>
+        <v>430.3</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>142.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1578.5</v>
+        <v>1587.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10712.8</v>
+        <v>18602.6</v>
       </c>
     </row>
     <row r="11">
@@ -2847,7 +2847,7 @@
         <v>971.8</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11684.6</v>
+        <v>19574.4</v>
       </c>
     </row>
     <row r="12">
@@ -2874,7 +2874,7 @@
         <v>840.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>12524.7</v>
+        <v>20414.5</v>
       </c>
     </row>
     <row r="13">
@@ -2885,19 +2885,19 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="7" t="n">
-        <v>7925.5</v>
+        <v>13835.5</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2878.7</v>
+        <v>4858.5</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1720.5</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>12524.7</v>
+        <v>20414.5</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>12524.7</v>
+        <v>20414.5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2619,19 +2619,19 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1671.2</v>
+        <v>836.4</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>573.5</v>
+        <v>287.3</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>139.3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2384</v>
+        <v>1263</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2384</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="4">
@@ -2646,19 +2646,19 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2204.6</v>
+        <v>1102.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>801.3</v>
+        <v>400.6</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>214.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3220.2</v>
+        <v>1717.3</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5604.3</v>
+        <v>2980.3</v>
       </c>
     </row>
     <row r="5">
@@ -2673,19 +2673,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>861</v>
+        <v>430.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>386.6</v>
+        <v>193.3</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>184.5</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1432.1</v>
+        <v>808.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>7036.3</v>
+        <v>3788.5</v>
       </c>
     </row>
     <row r="6">
@@ -2700,19 +2700,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1480.3</v>
+        <v>740.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>448.3</v>
+        <v>224.1</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>261.9</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2190.5</v>
+        <v>1226.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9226.799999999999</v>
+        <v>5014.7</v>
       </c>
     </row>
     <row r="7">
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1629.7</v>
+        <v>814.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>366.1</v>
+        <v>183.1</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>163.7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2159.5</v>
+        <v>1161.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11386.4</v>
+        <v>6176.3</v>
       </c>
     </row>
     <row r="8">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1983.5</v>
+        <v>991.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>639.5</v>
+        <v>319.8</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>104.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2727.7</v>
+        <v>1416.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>14114.1</v>
+        <v>7592.5</v>
       </c>
     </row>
     <row r="9">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1980</v>
+        <v>990</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>739.2</v>
+        <v>369.6</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>182.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2901.4</v>
+        <v>1541.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>17015.5</v>
+        <v>9134.299999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2820,7 +2820,7 @@
         <v>1587.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>18602.6</v>
+        <v>10721.5</v>
       </c>
     </row>
     <row r="11">
@@ -2847,7 +2847,7 @@
         <v>971.8</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>19574.4</v>
+        <v>11693.3</v>
       </c>
     </row>
     <row r="12">
@@ -2874,7 +2874,7 @@
         <v>840.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>20414.5</v>
+        <v>12533.4</v>
       </c>
     </row>
     <row r="13">
@@ -2885,19 +2885,19 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="7" t="n">
-        <v>13835.5</v>
+        <v>7931.1</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>4858.5</v>
+        <v>2881.7</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1720.5</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>20414.5</v>
+        <v>12533.4</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>20414.5</v>
+        <v>12533.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -2619,19 +2619,19 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1671.2</v>
+        <v>836.4</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>573.5</v>
+        <v>287.3</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>139.3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2384</v>
+        <v>1263</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2384</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="4">
@@ -2646,19 +2646,19 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2204.6</v>
+        <v>1102.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>801.3</v>
+        <v>400.6</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>214.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3220.2</v>
+        <v>1717.3</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5604.3</v>
+        <v>2980.3</v>
       </c>
     </row>
     <row r="5">
@@ -2673,19 +2673,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>861</v>
+        <v>430.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>386.6</v>
+        <v>193.3</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>184.5</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1432.1</v>
+        <v>808.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>7036.3</v>
+        <v>3788.5</v>
       </c>
     </row>
     <row r="6">
@@ -2700,19 +2700,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1480.3</v>
+        <v>740.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>448.3</v>
+        <v>224.1</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>261.9</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2190.5</v>
+        <v>1226.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9226.799999999999</v>
+        <v>5014.7</v>
       </c>
     </row>
     <row r="7">
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1629.7</v>
+        <v>814.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>366.1</v>
+        <v>183.1</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>163.7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2159.5</v>
+        <v>1161.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11386.4</v>
+        <v>6176.3</v>
       </c>
     </row>
     <row r="8">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1983.5</v>
+        <v>991.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>639.5</v>
+        <v>319.8</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>104.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2727.7</v>
+        <v>1416.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>14114.1</v>
+        <v>7592.5</v>
       </c>
     </row>
     <row r="9">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1980</v>
+        <v>990</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>739.2</v>
+        <v>369.6</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>182.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2901.4</v>
+        <v>1541.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>17015.5</v>
+        <v>9134.299999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2820,7 +2820,7 @@
         <v>1587.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>18602.6</v>
+        <v>10721.5</v>
       </c>
     </row>
     <row r="11">
@@ -2847,7 +2847,7 @@
         <v>971.8</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>19574.4</v>
+        <v>11693.3</v>
       </c>
     </row>
     <row r="12">
@@ -2874,7 +2874,7 @@
         <v>840.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>20414.5</v>
+        <v>12533.4</v>
       </c>
     </row>
     <row r="13">
@@ -2885,19 +2885,19 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="7" t="n">
-        <v>13835.5</v>
+        <v>7931.1</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>4858.5</v>
+        <v>2881.7</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1720.5</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>20414.5</v>
+        <v>12533.4</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>20414.5</v>
+        <v>12533.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4382</v>
+        <v>3956</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>30.3</v>
+        <v>27</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>10.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>48.8</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1750</v>
+        <v>1580</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>16.1</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>950</v>
+        <v>850</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>777</v>
+        <v>697</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.3</v>
@@ -642,7 +642,7 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6854</v>
+        <v>7597</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>75.7</v>
+        <v>83</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>15.3</v>
+        <v>16.9</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2000</v>
+        <v>1753</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>16.6</v>
+        <v>14</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>21.7</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4262</v>
+        <v>3910</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>27.8</v>
+        <v>24.9</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>36.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5384</v>
+        <v>5611</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>30.3</v>
+        <v>28.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>38.3</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3062</v>
+        <v>3283</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>29.8</v>
+        <v>33.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>35.7</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2590</v>
+        <v>2849</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>21.2</v>
+        <v>24.1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>32.9</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2100</v>
+        <v>1908</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>59.2</v>
+        <v>54.8</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>17.5</v>
+        <v>15.2</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>76.7</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2330</v>
+        <v>2249</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>60.3</v>
+        <v>54.6</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>18.8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>11.2</v>
+        <v>18.4</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>90.2</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1543</v>
+        <v>1613</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>35.4</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2428</v>
+        <v>2382</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>34.5</v>
+        <v>31.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3362</v>
+        <v>3432</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>26</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2226</v>
+        <v>2126</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1310</v>
+        <v>1108</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>14.2</v>
+        <v>11.1</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>10.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>24.9</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7150</v>
+        <v>7350</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>132.1</v>
+        <v>134</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>147.8</v>
+        <v>149.2</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3773</v>
+        <v>3840</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2753</v>
+        <v>2971</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="25">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1205</v>
+        <v>1220</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>63941</v>
+        <v>63935</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>467.9</v>
+        <v>451.2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>201.7</v>
+        <v>203</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>170.5</v>
+        <v>184.9</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>840.1</v>
+        <v>839.1</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>30.3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1450</v>
+        <v>1300</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>10.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>35</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>850</v>
+        <v>710</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="14">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>0.8</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0.5</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3600</v>
+        <v>3950</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>75.7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3200</v>
+        <v>3530</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>15.3</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>43.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1100</v>
+        <v>930</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>15.1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>16.6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="26">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>20.6</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2350</v>
+        <v>2100</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>11.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>27.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="29">
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>27.3</v>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2830</v>
+        <v>2670</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>30.3</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2280</v>
+        <v>2650</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>3.1</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>3.5</v>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1550</v>
+        <v>1750</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>29.8</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1500</v>
+        <v>1520</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="35">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="36">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1310</v>
+        <v>1400</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1250</v>
+        <v>1420</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>17</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>21.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>45</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1350</v>
+        <v>1250</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>59.2</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>17.5</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="41">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1270</v>
+        <v>1150</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>47.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>60.3</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="43">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="D44" s="4" t="n">
         <v>186.1</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>11.2</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="45">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>35.5</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>900</v>
+        <v>952</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>28.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>26.5</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>34.5</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1100</v>
+        <v>1130</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>11.5</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="50">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D50" s="4" t="n">
         <v>14.1</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="51">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1600</v>
+        <v>1610</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>5.8</v>
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1760</v>
+        <v>1820</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>6.8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>550</v>
+        <v>430</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>25.8</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>14.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>760</v>
+        <v>660</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>10.7</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>0</v>
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>950</v>
+        <v>850</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2700</v>
+        <v>2950</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3500</v>
+        <v>3550</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>37.8</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>132.1</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1700</v>
+        <v>1730</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1423</v>
+        <v>1360</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1350</v>
+        <v>1450</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>3.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>58.6</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="69">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>655</v>
+        <v>620</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="71">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.29.pdf</t>
+          <t>Revenue Meeting_2026.10.13.pdf</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.09.29</t>
+          <t>2026.10.13</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -2862,19 +2862,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>467.9</v>
+        <v>451.2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>201.7</v>
+        <v>203</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>170.5</v>
+        <v>184.9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>840.1</v>
+        <v>839.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>12533.4</v>
+        <v>12532.3</v>
       </c>
     </row>
     <row r="13">
@@ -2885,19 +2885,19 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="7" t="n">
-        <v>7931.1</v>
+        <v>7914.4</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2881.7</v>
+        <v>2883</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1720.5</v>
+        <v>1734.9</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>12533.4</v>
+        <v>12532.3</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>12533.4</v>
+        <v>12532.3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3956</v>
+        <v>4394</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>27</v>
+        <v>31.5</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>45.2</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3</v>
@@ -554,7 +554,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>3.3</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1580</v>
+        <v>1480</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>850</v>
+        <v>790</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>697</v>
+        <v>657</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.3</v>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7597</v>
+        <v>7640</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>83</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>105</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1753</v>
+        <v>1713</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3910</v>
+        <v>3950</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>24.9</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5611</v>
+        <v>5450</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>37.8</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3283</v>
+        <v>3373</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>33.7</v>
+        <v>35.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>39.7</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="14">
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2849</v>
+        <v>2811</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>36.4</v>
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2249</v>
+        <v>2232</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>54.6</v>
+        <v>52.2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>18.4</v>
+        <v>17.1</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>91.8</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1613</v>
+        <v>1638</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2382</v>
+        <v>2302</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>31.8</v>
+        <v>30.5</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>45.5</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3432</v>
+        <v>3382</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>26.6</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="20">
@@ -894,13 +894,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2126</v>
+        <v>2141</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>1.8</v>
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1108</v>
+        <v>1098</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7350</v>
+        <v>7430</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.1</v>
+        <v>10.7</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>6.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>134</v>
+        <v>130.3</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>149.2</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3840</v>
+        <v>3859</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2971</v>
+        <v>3171</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1220</v>
+        <v>1245</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>8.4</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>63935</v>
+        <v>64354</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>451.2</v>
+        <v>454.9</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>203</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>184.9</v>
+        <v>184.2</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>839.1</v>
+        <v>842.1</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>27</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="4">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>35</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="10">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>7.1</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>710</v>
+        <v>630</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0.5</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3950</v>
+        <v>4000</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>83</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3530</v>
+        <v>3500</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>43.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>15.1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1800</v>
+        <v>1840</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2670</v>
+        <v>2600</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2650</v>
+        <v>2530</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>3.1</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1750</v>
+        <v>1850</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>33.7</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1520</v>
+        <v>1510</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1420</v>
+        <v>1425</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>17</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>45</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="39">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>47.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>54.6</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1000</v>
+        <v>1040</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>18.8</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="44">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D44" s="4" t="n">
         <v>186.1</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>18.4</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="45">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>35.5</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>952</v>
+        <v>970</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>28.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>26.5</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>31.8</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1130</v>
+        <v>1100</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>11.5</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1610</v>
+        <v>1550</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D53" s="4" t="n">
         <v>124.1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="54">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>6.8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1350</v>
+        <v>1380</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>25.8</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>0</v>
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>9.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="61">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2950</v>
+        <v>2980</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>2.1</v>
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3550</v>
+        <v>3450</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>37.8</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>134</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="64">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1360</v>
+        <v>1329</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1450</v>
+        <v>1550</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>3.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="68">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="71">
@@ -2862,19 +2862,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>451.2</v>
+        <v>454.9</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>203</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>184.9</v>
+        <v>184.2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>839.1</v>
+        <v>842.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>12532.3</v>
+        <v>12535.4</v>
       </c>
     </row>
     <row r="13">
@@ -2885,19 +2885,19 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="7" t="n">
-        <v>7914.4</v>
+        <v>7918.1</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>2883</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1734.9</v>
+        <v>1734.2</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>12532.3</v>
+        <v>12535.4</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>12532.3</v>
+        <v>12535.4</v>
       </c>
     </row>
   </sheetData>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.10.13.pdf</t>
+          <t>Revenue Meeting_2026.10.20.pdf</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.10.13</t>
+          <t>2026.10.20</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2862,19 +2862,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>454.9</v>
+        <v>451.2</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>203</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>184.2</v>
+        <v>184.9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>842.1</v>
+        <v>839.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>12535.4</v>
+        <v>12532.3</v>
       </c>
     </row>
     <row r="13">
@@ -2885,19 +2885,19 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="7" t="n">
-        <v>7918.1</v>
+        <v>7914.4</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>2883</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1734.2</v>
+        <v>1734.9</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>12535.4</v>
+        <v>12532.3</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>12535.4</v>
+        <v>12532.3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2862,19 +2862,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>451.2</v>
+        <v>454.9</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>203</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>184.9</v>
+        <v>184.2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>839.1</v>
+        <v>842.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>12532.3</v>
+        <v>12535.4</v>
       </c>
     </row>
     <row r="13">
@@ -2885,19 +2885,19 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="7" t="n">
-        <v>7914.4</v>
+        <v>7918.1</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>2883</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1734.9</v>
+        <v>1734.2</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>12532.3</v>
+        <v>12535.4</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>12532.3</v>
+        <v>12535.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4394</v>
+        <v>4344</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>840</v>
+        <v>862</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1480</v>
+        <v>1390</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="7">
@@ -608,13 +608,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.3</v>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7640</v>
+        <v>7615</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>106.9</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1713</v>
+        <v>1723</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3950</v>
+        <v>3880</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>33.2</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5450</v>
+        <v>5499</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>1.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>36.7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3373</v>
+        <v>3388</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>5.3</v>
@@ -752,7 +752,7 @@
         <v>0.7</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2811</v>
+        <v>2706</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>24.2</v>
+        <v>22.9</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>36.4</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1908</v>
+        <v>1871</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>54.8</v>
+        <v>51.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>70.5</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2232</v>
+        <v>2218</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>52.2</v>
+        <v>51.3</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>19.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>17.1</v>
+        <v>18.2</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1638</v>
+        <v>1618</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>37.3</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2302</v>
+        <v>2286</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>43.8</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3382</v>
+        <v>3439</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2141</v>
+        <v>2106</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>4.6</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1098</v>
+        <v>1078</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>11.6</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7430</v>
+        <v>7435</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>6.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>130.3</v>
+        <v>127.4</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>147.1</v>
+        <v>145.1</v>
       </c>
     </row>
     <row r="23">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3859</v>
+        <v>3893</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>3.5</v>
@@ -972,7 +972,7 @@
         <v>3.9</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3171</v>
+        <v>3180</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1245</v>
+        <v>1310</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>14.8</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>64354</v>
+        <v>64158</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>454.9</v>
+        <v>448.2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>203</v>
+        <v>203.3</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>184.2</v>
+        <v>184.8</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>842.1</v>
+        <v>836.3</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2800</v>
+        <v>2780</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>35</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>7.1</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>11.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>7.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>850</v>
+        <v>765</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>10.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0.5</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4000</v>
+        <v>3920</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3500</v>
+        <v>3530</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>43.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>15.1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2100</v>
+        <v>2070</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>11.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1840</v>
+        <v>1800</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2600</v>
+        <v>2620</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2530</v>
+        <v>2575</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>3.1</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>3.5</v>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="34">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1350</v>
+        <v>1320</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1425</v>
+        <v>1350</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>17</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>24.2</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="38">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1250</v>
+        <v>1175</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>54.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="41">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>47.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>52.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="43">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D44" s="4" t="n">
         <v>186.1</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>17.1</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="45">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>35.5</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>28.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>26.5</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D50" s="4" t="n">
         <v>14.1</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="51">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>5.8</v>
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1820</v>
+        <v>1880</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="53">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D53" s="4" t="n">
         <v>124.1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="54">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>6.8</v>
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1380</v>
+        <v>1350</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="56">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="61">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3450</v>
+        <v>3375</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>37.8</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>130.3</v>
+        <v>127.4</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>800</v>
+        <v>842</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="64">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1730</v>
+        <v>1738</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>2</v>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1329</v>
+        <v>1313</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.2</v>
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>3.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="68">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>58.6</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="69">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>620</v>
+        <v>660</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="71">
@@ -2862,19 +2862,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>454.9</v>
+        <v>448.2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>203</v>
+        <v>203.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>184.2</v>
+        <v>184.8</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>842.1</v>
+        <v>836.3</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>12535.4</v>
+        <v>12529.5</v>
       </c>
     </row>
     <row r="13">
@@ -2885,19 +2885,19 @@
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="7" t="n">
-        <v>7918.1</v>
+        <v>7911.4</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2883</v>
+        <v>2883.3</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1734.2</v>
+        <v>1734.8</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>12535.4</v>
+        <v>12529.5</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>12535.4</v>
+        <v>12529.5</v>
       </c>
     </row>
   </sheetData>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.10.20.pdf</t>
+          <t>Revenue Meeting_2026.10.27.pdf</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.10.20</t>
+          <t>2026.10.27</t>
         </is>
       </c>
     </row>

--- a/docs/data/소사업_예상매출.xlsx
+++ b/docs/data/소사업_예상매출.xlsx
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 예상매출 - 2026-10  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
+          <t>소사업 예상매출 - 2026-11  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4344</v>
+        <v>4750</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>31.2</v>
+        <v>53.3</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>11</v>
+        <v>23.9</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>51.2</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>862</v>
+        <v>1142</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4.9</v>
+        <v>12.4</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1</v>
+        <v>8.6</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1390</v>
+        <v>1173</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.9</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="8">
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>647</v>
+        <v>760</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7615</v>
+        <v>6960</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16.9</v>
+        <v>36.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.1</v>
+        <v>5.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>106.5</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1723</v>
+        <v>1672</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>18.3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3880</v>
+        <v>3800</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>24.5</v>
+        <v>40.6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>32.6</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5499</v>
+        <v>5154</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>37</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3388</v>
+        <v>3128</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>35.8</v>
+        <v>27.9</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>41.8</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2706</v>
+        <v>3463</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10.4</v>
+        <v>21.3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>22.9</v>
+        <v>15.2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>34.9</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1871</v>
+        <v>1850</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2218</v>
+        <v>2157</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>51.3</v>
+        <v>43.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>19.5</v>
+        <v>13.6</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>18.2</v>
+        <v>3.8</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>89</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1618</v>
+        <v>1485</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>15.1</v>
+        <v>21.4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.1</v>
+        <v>0.3</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>36.5</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2286</v>
+        <v>1900</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>30</v>
+        <v>43.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>12.6</v>
+        <v>17.7</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>43.3</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3439</v>
+        <v>2427</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>17.6</v>
+        <v>6.3</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>28.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2106</v>
+        <v>1586</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1078</v>
+        <v>1251</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>11.6</v>
+        <v>17.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>12.4</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>20.3</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7435</v>
+        <v>9750</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>11.5</v>
+        <v>14.7</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>127.4</v>
+        <v>224.2</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>145.1</v>
+        <v>244.6</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3893</v>
+        <v>2998</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3180</v>
+        <v>2350</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1310</v>
+        <v>1050</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>64158</v>
+        <v>62306</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>448.2</v>
+        <v>490.6</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>203.3</v>
+        <v>190</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>184.8</v>
+        <v>279.4</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>836.3</v>
+        <v>960</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 세그먼트별 - 2026-10</t>
+          <t>소사업 세그먼트별 - 2026-11</t>
         </is>
       </c>
     </row>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2780</v>
+        <v>3650</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>11.2</v>
+        <v>14.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>31.2</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1250</v>
+        <v>900</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>314</v>
+        <v>200</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>35</v>
+        <v>119.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>11</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>435</v>
+        <v>850</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.2</v>
+        <v>14.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.9</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>425</v>
+        <v>220</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>35</v>
+        <v>119.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>11.2</v>
+        <v>14.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>470</v>
+        <v>400</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>35</v>
+        <v>119.5</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>765</v>
+        <v>700</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>625</v>
+        <v>470</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>370</v>
+        <v>250</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="D18" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0.3</v>
       </c>
     </row>
     <row r="19">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0.5</v>
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>29.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3920</v>
+        <v>3400</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>21</v>
+        <v>15.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3530</v>
+        <v>3450</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>16.9</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>43.3</v>
+        <v>47.1</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="24">
@@ -1550,10 +1550,10 @@
         <v>900</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>820</v>
+        <v>750</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2070</v>
+        <v>2100</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>11.8</v>
+        <v>19.4</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>24.5</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>27.3</v>
+        <v>49.1</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2620</v>
+        <v>2600</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2575</v>
+        <v>2300</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>304</v>
+        <v>254</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.5</v>
+        <v>22.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1860</v>
+        <v>1450</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>35.8</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1515</v>
+        <v>1650</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="35">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="36">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1320</v>
+        <v>1755</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>7.8</v>
+        <v>12.1</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.4</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1350</v>
+        <v>1680</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>22.9</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>45</v>
+        <v>40.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="41">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1080</v>
+        <v>1150</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>47.5</v>
+        <v>38</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>51.3</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>18.8</v>
+        <v>14.3</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>19.5</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="44">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>186.1</v>
+        <v>65.8</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>18.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="45">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>425</v>
+        <v>480</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>35.5</v>
+        <v>44.6</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>15.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>980</v>
+        <v>800</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>28.7</v>
+        <v>1.5</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>6.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1130</v>
+        <v>900</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>26.5</v>
+        <v>48.6</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>30</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>11.5</v>
+        <v>17.7</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>12.6</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="50">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>14.1</v>
+        <v>64.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1545</v>
+        <v>1250</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1880</v>
+        <v>1150</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>17.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="53">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>124.1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1350</v>
+        <v>950</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="56">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>25.8</v>
+        <v>34.4</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>11.6</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>620</v>
+        <v>700</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>14</v>
+        <v>17.7</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="59">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>0</v>
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1080</v>
+        <v>1200</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>11.5</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2980</v>
+        <v>2550</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3375</v>
+        <v>6000</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>127.4</v>
+        <v>224.2</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>842</v>
+        <v>560</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>5.8</v>
+        <v>11.4</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1738</v>
+        <v>1250</v>
       </c>
       <c r="D64" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E64" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>3.5</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1313</v>
+        <v>1188</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1595</v>
+        <v>1100</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1560</v>
+        <v>1250</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="68">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>58.6</v>
+        <v>6187</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>660</v>
+        <v>600</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="71">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2566,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 월별 누적 - 2026-10 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+          <t>소사업 월별 누적 - 2026-11 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
         </is>
       </c>
     </row>
@@ -2858,46 +2858,73 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>온북</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>449.3</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>205.7</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>842.9</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>12536.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11월</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>RM FCST</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>448.2</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>203.3</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>184.8</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>836.3</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>12529.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="n">
+        <v>490.6</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>960</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>13496.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="7" t="n">
-        <v>7911.4</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>2883.3</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>1734.8</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>12529.5</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>12529.5</v>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="7" t="n">
+        <v>8403.1</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>3075.7</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>2017.3</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>13496.1</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>13496.1</v>
       </c>
     </row>
   </sheetData>
@@ -2926,7 +2953,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2965,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전년 2025-10 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-11 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>
